--- a/bioinf_SP/28s_18s.xlsx
+++ b/bioinf_SP/28s_18s.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/vkr_mag/NEW_28s/FINAL_dir/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/vkr_mag/rep_SP/bioinf_SP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D14B2C-4132-A84B-B574-EC4352F72BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE368C8-3D80-F74B-9C6C-F412F155A9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="1300" windowWidth="25480" windowHeight="16860" xr2:uid="{2F5F73E2-281A-CB4D-BB1C-DC3B7C715EAB}"/>
+    <workbookView xWindow="3960" yWindow="600" windowWidth="22280" windowHeight="15220" xr2:uid="{2F5F73E2-281A-CB4D-BB1C-DC3B7C715EAB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="seq" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="388">
   <si>
     <t>id</t>
   </si>
@@ -2491,34 +2491,13 @@
     <t>Ib8</t>
   </si>
   <si>
-    <t>Elena</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
-    <t>ACCTGGTTGATCCTGCCAGTAGTCATATGCTTGTCTCAAAGATTAAGCCATGCATGTCTAAGAATAAGCCCTAGCACGGTGAATCTGCGAATGGCTCATTAAATCAGTTATTGTTTATTTGATGAAATGAATTTTTTTTAAAAAATTTACTACTTGGATAACCGTAGTAATTCTAGAGCTAATACATGCGATTAAGCCTTGCCTTTCTCCTTTCGGGGAGGGAGAACAGGTGCATTTATTAGATTTAAACCATCGGTTTTTGTCCTTTTTTCTTTCGGGGAGGAGGGGCATTTCATAAACCTTTAATGGCGAGTCATAATAACTGAGCGAATCGAACTTTTTGGTCTTCCTTCACTGGCGGACTGGTCGATACCTCATTCAAATTTCTGCCCTATCAGCTTTCGATGGTAGGATCTTGGCCTACCATGGCTATAACGGGTAACGGGGAATTAGGGTTCGATTCCGGAGAGGGAGCTTGAGAAACGGCTACCACATCCAAGGATGGCAGCAGGCGCGCAAATTACCCAATCCCGACACGGGGAGGTAGTGACAATAAATAACAACGCCGGACTATCTTTAGTCTGGCGATTGGAATGAGAGTAATTTAAACCAATTCTCGAGTAACCATTGGAGGGCAAGTCTGGTGCCAGCAGCCGCGGTAATTCCAGCTCCAATAGCGTATATTAAAGTTGTTGCAGTTAAAAAGCTCGTAGTCTGAACTATGGCTGGTGATTTTTGCTTGTGTCCATGGGCTTTTTGCCTTTCATTTGCTTCCCTTTCCTCTTGATTTCTTTTCTCTTTTTTGGGATTAGTTTTCGAGGGTTAGATGAGGCGGTGTTTCTGTGCATTTGCTCGTGTTGTATACGGCAACTCCAGCCTCTTTTAATAAGCATTTTTTTAAGTGTTTTGTTTGTACTTCAGAGGATCGTTTGTGCTTTTAACTAAGTACTTTCAGGATTCTGATTGTTTACTTTGAGAAAAATAGAGTGTTCAAAGCAGGCGACTTTTAGTTCGCACAAATTTATATTGAATACATTAGCATGGGATAATAAAATAGGACATTGAGCCTACTTTGGTGGTAGTTTCTTTGGGGGGGAGAGACTTTTGTTTCCTTCCTCCATTGGAGATAAAGGGTCGATGTAATGATTAAAAGGAACAGTTGGGGATATCAATACTCTACGGCTAGAGGTGAAATTCTTTGATTCGTGGAAGATTAACTACTGCGAAAGCATTTATCAAAGATGTTTTCATTGATCAAGAACGAAAGTTAGGGGAGCAAAGACGATCAGATACCGTCGTAGTCTTAACCATAAACGATGCCGACTAGGGATCAGCGGGCGTTAGTTATTTTTACATGACTCCGTTGGCACCTCCTCCCATGAGAAATCTTTAAGTCTTTGGGTTCCGGGGGGAGTATGGTCGCAAGGCTGAAACTTAAAGGAATTGACGGAACAGCACACCAGATGTGGAGCCTGCGGCTTAA</t>
-  </si>
-  <si>
-    <t>AACGACTTTCAACAGTGGATCTCTTGGCTCGTGTATCGATGAAGAACGCTGCGAACTGCGATACGTAATGCGAATTGCACAACTCAGTGAGTCATTGAAATTTTGAACGCATATTGCGCTGCGGCAGGGGGTTAAACCAATGCCGTAGCATGTTTGGTCGAGTGTTGTTTCCAAACCCTTTTTTTCTCTTTTTTTCTCAAAAGAACTAAAAAGGTTGTTGACCTGTGTTTCCCCTCAGAGCTTCTCCCTTCTTTTGCTTCCTTCTTGGATTAAAAAGAGAGAGCTCCGTCATGGTTTAAATCAAAAAGTTTTCCTTTTTAAAAGGAAAGGGTCTTTACTTTTTACACTTAAAGCGGTAAACTTTCATCACTTTTAGCGAAAAAGCAATCTCCCGTCCTCTTTTTATTTGGATTAACCTCGACTCAAGCAAGATTACCCGCTGAATTTAAGCATATCACTAAGCGGAGGAAAAGAAACTAACAAGGATTCCCCTAGTAACGGCGAGTGAAGAGGGAACAGCTCAAGCTTAAAACCTGCGTCTATCCTTGTGTTGCTTTTGGAATGCTTGGACATAAGACGTCGGATTGTAGCCTAAAGAAAATCCCATCCTTCTTAGGGCAAAATGTATCAAAGTTTAGTGACCTAAGTGCCTTGGAACAGGCTGCCATGGAGGGTGAGAGCCCCGTTCGAGGTCACCCTTTTGCCCTATTTATTGTTAAGTGATGTTTTTTCGTCGAGTCGGGTTGCTTGAGAGTGTAGCCTTAAGTGGGTGGTATACTTCATCTAAAGCTAAATATTAACACGAGACCGATAGCGAACAAGTACCGTGAGGGAAAGATGAAAAGAACTTTGAAAAGAGAGTTAAAAGTACGTGAAACTGTTGAAAGGGAAGCCGATAGAATCAGAGTCTCGTACGGCTCTTTCTTCCTTTTTTGGAAGCTTAACGAGTCGGGGCCTTTGGATGCATTAAACCTGTGTGAAATAGCTCCCTGGGTTAGGTAGGAGTTCCCTTGCTTTCTTGGCAAAGGCTTCGAAATCCCTTTGGAGATTTTTACGTCGGCAGTGTTTGATGGAGGACAGAGTGAAGAGCTCGGCGTTTGTTCGCCACTGTAGTTTTCTGGATTAGCTTTGGCAAGGTGAATACTCATTTTGTTTTATACTTCATCTCGAAGTCTTTAACGAGTTTTAAAATGTTATCTTAGCTGGCTTTTTCTCTACCTTTTGTAGCTCTTTAGATCCAAAGTTTAATGGTTTTATCGGGCCCGTCTTGAAACACGGACCAAGGAGTCTAACATTAAAGCAAGTCGTAGAGTGTAAAACTTGTTTAAAGAGGAGGGATTTTCCTTTCTCTTTTTTTAAAGGCGTAATGAAAGTAAAAGGCTTTGGAAAACCAAGGCACGTTTGAGGTGAGACCCGGCGTTTCTTTCCCCTTAAAAGGAAGGAAGTAAAGGAGCATCATCAACCGATCATGATCCTCGGTGATTGATTTGAGTGAGAGCTTTAATGTTGGTACCCGAAAGATGGTGAACTATGCCTGTATAGGGCGAAGCCAGAGGAAACTCTGGTGGAAGCTCGTAGCGATACTGACGTGCAAATCGTTCGTCAAATGTGGGTATAGGGGCGAAAGACTAATCGAACCATCTAGTAGCTGGTTCCCTCCGAAGTTTCCCTCAGGATAGCTGGAACTCGAGTTTAATTTATTACACTTAGTCTTGTCAGGTAAAGCGAATGATTAGAGGACTCAGGGATGAAACATCTTTGACCTATTCTCAAACTTTAAATGGGCAAGAAGTCCCTGTTTCTTAAGTGAACTTGGGCGAAAAGTCGTGAGGCTTTTCATTTTTTTGGATATATGAGTTCTTAGTGGGCCATTTTTGGTAAGCAGAACTGGCGATGTGGGATGATCCGAACGTTGAGTTAAGGCGCCAAACTATGCGCTCATCAGATACCACAAAAGGTGTTGGTTGATACAGACAGCAGGACGGTGGCCATGGAAGTCGGAATCCGCTAAGGAGTGTGTAACAACTCACCTGCCGAATCAACTAGCCCTGAAAATGGATGGCGCTTAAGCGCATGGCCTATACTCAACCGTCATTGTATTAAAATTTTTTTGTTTATTTCATAAAGCAGAATAGTGAGACTTTGACGAGTAGGAGGGCGTGGCGGTCTAGTTTTAAATTGAAAGTAGAAATCCTTTTTATTTTTTTTAAAAGCAACGAAGCCCAAAATTCAAGTCATTTTTTTTAAATGTTAAAGGGCGCAAGCCCGGGTGAAGCGGCCGCTAGTGCAGATCTTGGTGGAAGTAGCAAATATTCAAATGAGAACTTTGAAGACTGAAGTGGAGAAAGGTTCCATGTGAACATCGATTGGACATGGGTTAGTCGATCCTAAGTGATAAGCGAAAGCTGTTCTGAATTACTTTTCAAAATACTTTTCTGTATTTTAAAGAGGAACGAAAGGGAATTGGGTTAATATTCCCAAACCTGCAAGAGATACAACTTGTTTTCCTTCTTTTTGGGGGGAAGCAATATATTGCGGCAACGCAAACGAACATGGAGATTTTGCCGGCCAAGGCCCCTGAAAGAGTTATCTTTTCTTATTAACAAGCTTTTATTAACTAATCATTTTTTTTAGTGACCATGGAATCGTATTATACGGAGATATGGTTGTATGCTTGGTAAAGCAGGTCGATTCTTGACTTGTCGGGTGCGTTTTGGACGGTCCTTGAAAATCCATGGGAGATTCTTTAATTTTTCTTGCTGGTCGTACTCATAACCGCATCAGGTCTCCAAGGTGATCAGCCTCTAGTCAATAGAATAATGTAGGTAAGGGAAGTCGGCAAAATAGATCCGTAACTTCGGGAAAAGGATTGGCTCTGAAGGCTGGGCTAAGGGATCCACTGCGCGGGGATTGGTTTTTTTGCCTTAATTTATGCTGGGAGCTAAGGCACCGGGACCCCTCTTCTGAGGGGACCTAGAGCTTTGGAACCCGCTATCACTAGGCCCTTTCTCTTTAGTGCTTTGGAAAACGTGCCCATTTTCTTTTTTTTTTTCTTTTCGGAGAGGAAGGAGAGGAAATATGGGGTCAAACACCTCGCTCTCTTAGCAATTAACAGCTAATTCAGAACTGTTTCGGACAAGGGGAATCCGACTGTTTAATTAAAACAAAGCATTGTGATGGTCGTTGGACGATGTTGACACAATGTGATTTCTGCCCAGTGCTCTGAATGTCAAAGTGAAGAGATTCAACCAAGCGCGGGTAAACGGCGGGAGTAACTATGACTCTCTTAAGGTAGCCAAATGCCTCGTCATCTAACTAGTGACGCGCATGAATGGATTAATGAGATTCCCACTGTCCCTATCTACTATCTAGCGAAACCACAGCCAAGGGAACGGGCTTGGAAACATCAGCGGGGAAAGAAGACCCTGTTGAGCTTGACTCTAGTCAGACTTTGTGAATTGACTTGGAAGGTGTAGAATAAGTGGGAGTTTGCTTTACTGTAAACGTCAATGAAATACCACTACTTCCACTGTCACTTTACTTATTTAATCGTGCAGAAAGATAGCTTGTCTGCTTTTTTTCTCTTTGTCTTCTTCGGAAGGTAAGGAGGAGGGAACAGAATTTAACGCTTCTTTGTAGTTTTAATCGTTGGGATTTTTCCCCCGCAAGGGGGAAGGTCCTTGAGATCTGTTTTAAAAACATTGTCTGGTGGGGAGTTTGGCTGGGGCGGCACATCTGTTAAAAGATAACGCAGGTGTCCTAAGATGGTCTCAATAAGAACAGAAATCTTATGTAGAGGAAAAGGCCAAAGTGACCATTTGATTTTGATTTTCAGTACGAATACAAACTGTGAAAGCATGGCCTATCGATCCTTTAGCGCTTGTAAGTATCAAGCTAGAGGTGTCAGAAAAGTTACCACAGGGATAACTGGCTTGTGGCAGCCAAGCGTTCATAGCGACGTTGCTTTTTGATCCTTCGATGTCGGCTCTTCCTATCATTGCGAAGCAGAATTCGCCAAGTGTTGGATTGTTCACCCACTAATAGGGAACGTGAGCTGGGTTTAGACCGTCGTGAGACAGGTTAGTTTTACCCTACTGATAAGCTTTTTTATTACAACAGTAATCCAGTTTAGTACGAGAGGAACCGCTGGTTCAGACAATTGGTTTATACGTTTGATTGAAAAATCATTGATGTGATGCTACCATCTGCAGGATTATGGCTGAACGCCTCTAAGTCAGAATCCATGCTGAAAAGTGATGAGATTAGATGGGGGTTTACCCTCCTGTCTATGTTGGCCCGAACAAGTTTTTTCGTAATTGGAAATTTTCGTCCCTGGTCTTTACGGCCTTGGACGCAGAGTTGAAGTAATCATAGACTCTCTTTTTAAAGGGGAAGTCAGAGACCATTGAGTTCTCAGCGTCGGTAGAGGCAAGTGCGGAAGTGTTTGTAAGTCTTGAAGCTTTGAGTGCTTGAATGCATTGAAATTATGTTCGGGTTCCGATAAATCCTTTGTATACGACTTAAATATTGGAACAAGGTATTGTAAGGGGTAGAGTGATCTTGTTGTTGCGATCCTTTGAGGTTCAGCCTGTC</t>
-  </si>
-  <si>
     <t>18s_seq</t>
   </si>
   <si>
     <t>28s_seq</t>
-  </si>
-  <si>
-    <t>ACCTGGTTGATCCTGCCAGTAGTCATATGCTTGTCTCAAAGATTAAGCCATGCATGTCTAAGAATTAGCCCACTTTGAACGGCGAATCTGCGAATGGCTCATTAAATCAGTCATTGTTTATTTGATGGTACCATTTCACACATGGACTAGTTGGACAACCGTAGTAATTCTAGAGCTAATACATGCCGATGATCCCTGAACGCGGGCGAAAGTCTGCTGCGCAGGGGAGCATTTATTAGATTCAAACCGTTGGGTAGCGAGCTATCAATGGTGAGTCAGAATAACTCAGCGGATCGGGAGCAAGGGGTGAATTGGGGAATTGATTTTTGTCAATTTCGCGTTTCACCCCCCCGACGCATCATTCAAATTTCTGCCCTATCAGCTTTCGATGGTAGGATCTTGGCCTACCATGGCGATCACGGGTAACGGGGAATTGGGGTTCGATTCCGGAGAGGGAGCTTGAGAAACGGCTACCACATCCAAGGATGGCAGCAGGCGCGCAAATTACCCAATCCCGACACGGGGAGGTAGTGACAATACATAACAATGCCTTTATATGTAGCCCTCACGGGTTACGGAGGCAATTGGAATGAGAGTGCGACAAACGTGAGCATTGTGTAAAGCGACTCTCGAGGAGCCATTGGAGGGCAAGTCTGGTGCCAGCAGCCGCGGTAATTCCAGCTCCAAGAGCATATATTAACATTGTTGCAGTTAAAAAGCTCGTAGTCTGAGAGAACGGTTAGGACGTGGATGGACGGATTAAACGGGATTCCGTTTTGATTCGTTGTTTTATTCACGTGCTGGCCTTGTTGTGTGTGTTTTGCACACACAACACGTTTCGTGGAGTGGGTACAATTGAATTGTATCCAGGTCTGCGATAGTTTACTTTGAGAAAAATAGAGCGTTCAAAGCAGGCGTTGACAAATGATAGCCTTGGTTTGTGTGTGGACTTCATCACATTGATGAGAAGATCACATGCGATTTGAATGTATTAGCATGGGATAATGGAATAGGACATTGGCTCTGTGTTTTCATCGCACGCCAGCCGTAACTTTGCTTACGCTTTTCGTAAGGGTTCGAGGGCCGATGTAATGGTCAACAGGGACAGTTGGGGAGATTCATACTCCATGGCTAGAGGTGAAATTCTTGGATTCATGGAAGATGAACTAGTGCGAAAGCATTTGTCAAAGATGCTTTCATTGATCAAGAACGAATGTTAGGGGAGCAAAGACGATCAGATACCGTCGTAGTCTTAACCATAAACGATGCCGACTCGGGATTGGGGGGCGCGGCGGGGGGGTGTGAACGGGTGTAAAAACCCTTACATCCCCCCAATCAGCCCCCCCAGCACCTCCGTTAACAATTACACGCAAGGGAAACCGATAAGTGTTTGGGTTCCGGGGGGAGTATGGTCGCAAGGCTGAAACTTAAAGGAATTGACGGAAGGGCACCACCAGGAGTGGAGTTTGCGGCTTAATTTGACTCAACACGGGGAAACTCACCAGGTCCAGACATGGCAAGGATTGACAGATTGAGAGCGCTTTCTTGATTCCGTGAAAGGTAGCGCATGGCCGTTCTTAGTTGGTGGAGTGATTTGTCTGGTTAATTCCGTTAACGAACGAGACCTTGGCCTGCTAACTAGTTGGGAGGGCGGGGGCGGGGGAGAGGGAGTGGATGTATGTAATGTATGTTTGCTATCTCTGCCCTGTCCACAACACCGCACTTTTTCGTGGTTAGCTCACAAAAGCTAGGCACAGCACAACTTCTTAGAGGGACAACCTGCATTTTAGCAGAGGGAAGCGAAAGGCGATAACAGGTCTGTGATGCTCTTAGATGTCCTGGGCTGCACGCGTACTACACTGACGAATGCAACGAGCATTGCCGGGGAAACATATGGAGCAATCCACTGTGTTTTCCCCTCCCTTGGCAGAAATGTCTGGGCAATCTTATTAACATTCGTCGTGCTGGGGATAGACGATTGCAATTATTTGTCTTGAACGAGGAATTCCTAGTAAGTGTGAGTCATCAGGTTGCGCTGATTACGTCCCTGCCCTTTGTACACACCGCCCGTCGCTCCTACCGATTGAATGGTCCGGTGAGAACATCGGATGGACTGCGCAAGTTGGAATGGGTATTTACTGCCTGTCTCCACAGCGTGGACCAGAAGTAGTTCAAATCTTACTATTTAGAGGAAGGAGAAGTCGTAACAAGGTTTCCGTAGGTGAACCTGCGGAAGGATCATT</t>
-  </si>
-  <si>
-    <t>CAGAGCAAATGCTTCTATCGGGCCCGTCTTGAAACACGGACCAAGGAGTCTAACATGTATGCGAGTCGTTGGGTGGAAAACCTGGAACAAATAAAAGGCGGAATGAAAGTGAATGTGTGGTGGTTGGACGAACAAATAGTTTCGTCTTCTCCATCAGCCGACCATGAACTAAGATGAGTGGTTTGAGTTTGAGCATATATGTTGGTACCCGAAAGATGGTGATCTATGCCTGTGCAGGGCGAAGCCAGAGGAAACTCTGGTGGAGGCTCGCAGCGATACTGACGTGCAAATCGTTCGTCAAATATGGGCATGGGGGCGAAAGACTCATCGAACCGTCTAGTAGCTGGTTCCCTCCGAAGTTTCCCTCAGGATAGCAGGCGCTTGACAATGAAATATGTTGTGTAGTCTTGTCAGGTAAAGCGAATGACTAGAGGACTCGGGGATGAAATATCCTCGGCCTATTCTCAAACTTTAAATGGGCAAGTGTGTTGCACATGCAGTTTCTTAAGTGAACTGAGTGCACTCAATATGATACAAAGCGCCTAGTGGGCCAATTTTGGTAAGCAGAACTGGCGATGTGGGATGAACCAAACGTCGAGTTAAGGCGCCCAAGTGCGCGCTCATCAGACCCCAGAAAAGGTGTTGGTTGATATGAACAGCAGGACGGTGGCCATGGAAGTCGGAACCCGCTAAGGAGTGTGTAACAACTCACCTGCCGAATCAAGCAGCCCTGAAAATGGATGGCGCTCAAGCGCGCGGCCCATACTCGACGGGGGGTGGTAGTGGATGAATATCCAAAAAGTCCATCCCCCTGTAGGAGGGCGTGGTGGTTATTAACCCTTGATGCTGATTGAGTTACAGCGGGGGTGTGTGCAGAGCAAGCAAGGGACAGCAATGCAAACTTGTTTTTGTTCCCCTTTTGCTCTGTGCAGTCGCGGAGAAGCCGATCAGGCGTGAGCCTGGGCGAAGCGGCCACCAGTGCAGATCTTGGTGGGAGTAGCAAGTATTCAAATGGGAACTTTGAAGACTGAGGTGGAGAAAGGTTCCATGTGAACAGTGATTGGACATGGGTAAGTCGATCCTAAGAGATAGGCGAAAGCTGTGGAAATGCGGAGCATTGATAAGCAATTATTGTGTGCTCCCGCTTATCGAAAGGGAACCAGGTCAAAATTCCTGGACCTGCGGAAGACTGAACACGAGAAAATGCTATGTATTTGCGTAGCGTTCTCTCTGACAAGCGGCAACGCTGAACGAACACGGAGAGAGTATTGTCGGCCAGTGCCCCTGGAAGAGTTGTCTTTTCTTGTTAACAAGCAAATAGCAATGAACACATTTTGTGTTTATTGCCTTGTCGCAACCGTGGAATCAGATTAGCTGGAGAGACGGTTGGGAAGCTTGGGAAAGCAGATCGGTTATTGGTCTGTCAGGAGCGTGCTGGACGGCCCTTGAAAATCCGTGGGAGAGAGGGGTGGGAAGTAATTCCCACACTGATAGTTTTTCCGCAACGGCGGTGTACCCTCGTAACAGAGGGTATTGCTCAGCCAGGTCGTACTGATAACCGCATCAGGTCTCCAAGGTGATCAGCCTCTAGTGGCAATAGAACAATGTGGATAAGGGAAGTCGGCAAAACAGATCCGTAACTTTGGGAAAAGGATTGGCTCTGAAGGCTGGGGACTTGCATAGCAGCTTTTTGCAAACGTGGATCCGTGCGATCGAGTGTGTGATTGTGGTTGTGTGTTGCGTGTACGCAGAGCGCAAGCTTTGTGTCGTGTGACACATATGCACACACACATTGGATCAAACACAGTGCGGAGAGGTGTGTGTATGTGCGGGTAGTCAAATACTTGTGTGTGCATATGTCTAAACACGGTGCAGTCCGGTTGGACAAAGTCATATTTGTCCATTATGAACAGCCAGTTCAGAACTGTTTCGGACAAGGGGAATCCGACTGTTTAATTAAAACAAAGCATTGCGAATTTATGTGGTCGTTGGATCGATGTAGACGCAATGTGATTTCTGCCCAGTGCTCTGAATGTTACAGTGAAGAGATTCAAGCAAGCGCGGGTAAACGGCGGGAGTAACTATGACTCTCTTAAGGTAGCCAAATGCCTCGTCATTTGATTGGTGACGCGCATGAATGGATTAATGAGATTCCCACTGTCCCTATCTGCTATCTAGCGAAACCACAGCCAAGGGAACGGGCTTGGAAGCATCAGCGGGGAAAGAAGACCCTGTTGAGTTTGACTCTAGTCAGGCTTTGTGAGTTGACTTGGAAGGTGTAGAATAAGCGGGAGGGGGAGTGCATGCAAATGTGTTTTCTCGACAATGAAATACCGCTACTGCCAATGTCAGTTTGCTTATTTAATGATTTGGGGTGGGTTGTTTGGCGGGGCCATGTGTGTGTGTTTTTCGCATGCACATCCCGTCCCCCTTTTTTGCTTTGAACCGCTGTCTGACGTCACAAGTCAGGCACAATGGGAAACTTCATGTAATCCCGCAAAGCCCCATTTTAGTGACCGAGTCTGGTGGGGAGTTTGGCTGGGGCGGCACATCTACTAAACGGTAACGTAGGTGTCCTAAGATGGTCTCAATGAGAACAGAAATCTCATGTGGAGGAAAAGGCCAAAGTGACCATTTGATTTTGATTTCCAGTACGAATACAAACTGTGAAAGCATGGCCTATCGATCCTTTGGAGGAGTGTGCGGCGTGAGGGTTTTTTCTCGCGCCGTGACTTGGGAGTACTTTGATTCAAGCCAGAGGTGTCAGAAAAATTACCACAGGGATAACTGGCTTGTGGCAGCCAAGCGTTCGCAGCGACGTTGCTTTTTGATCCTTCGATGTCGGCTCTTCCTATCA</t>
-  </si>
-  <si>
-    <t>ACCTGGTTGATCCTGCCAGTAGTCATATGCTTGTCTCAAAGATTAAGCCATGCATGTCTAAGAATAAACTCTTGAATGGTGAATCTGCGAATGGCTCATTAAATCAGTTATAGTTTATTTGATGGTACCTTACTACATGGATAACCGTAGTAATTCTAGAGCTAATACATGCGTAAAGCCCCATTCGGGGTGCATTTATTAGATTCAAACCATCGGCTCTTCACGGGGCCTTTGATGGTGAGTCATAATAACTGAGCGAATCGAATGGCCTTGTGCCGTCGATGCTTCATTCAAATTTCTGCCCTATCAGCTTTCGATGGTAGGATCTTGGCCTACCATGGCTATAACGGGTAACGGGGAATTAGGGTTCGATTCCGGAGAGGGAGCTTGAGAAACGGCTACCACATCCAAGGATGGCAGCAGGCGCGCAAATTACCCAATCCCGACACGGGGAGGTAGTGACAATAAATAACGATGCTGGACTATCATAGTCCGGCAATTGGAATGAGAGTAATTTAAATCAATACTCGAGGAGCCATTGGAGGGCAAGTCTGGTGCCAGCAGCCGCGGTAATTCCAGCTCCAATAGCGTATATTAAAGTTGTTGCAGTTAAAAAGCTCGTAGTCTGAATCTTGGTCGGTATTGAGCGTCCGTGGCTTTGCGGTCACGTGTATGCGATATTATACCGGCCCAATAACCCTTCGGAGGAACACGGGTGCTTTTAATTAAGTGCTCGTGGGATTCCGATAGTTTACTTTGAGAAAAATAGAGTGTTCAAAGCAGGCGTTTTTGCCGTTGAATACATTAGCATGGGATAATAGAATAGGACATTGGTTCTATTTTGATGGTTTACGGACCGATGTAATGATTAATAGGAACAGTTGGGGACATTCATATTCTATGGCTAGAGGTGAAATTCTTGGATTCATGGAAGATGAACTACTGCGAAAGCATTTGTCAAAGATGTTTTCATTGATCAAGAACGAAAGTTAGGGGAGCAAAGACGATCAGATACCGTCGTAGTCTTAACCATAAACGATGCCGACTAGGGATCGGTGGGAGTTAGTATTATGACTCCATCGGCACCTCATGGGAAACCAAAGTCTTTGGGTTCCGGGGGGAGTATGGTCGCAAGGCTGAAACTTAAAGGAATTGACGGAAGGGCACCACCAGGAGTGGAGCCTGCGGCTTAATTTGACTCAACACGGGAAAACTCACCAGGTCCAGACATGGTAAGGATTGACAGATTGAGAGCTCTTTCTTGATTCCATGAAAGGTGGCGCATGGCCGTTCTTAGTTGGTGGAGTGATTTGTCTGGTTAATTCCGATAACGAACGAGACCTTGACCTGCTAACTAGTCACGATAAGCTTTTTGCTTGTTGGTTGACTTCTTAGAGGGACAATCTGTTTCCAGCAGGTGGAAGTTTGAGGCAATAACAGGTCTGTGATGCCCTTAGATGTCCTGGGCTGCACGCGCGCTACACTGACGAACTCAACGAGTTTATCACCTTGACAGAGATGTCTGGGTAATCTTTTAAAAGTTCGTCGTGATGGGGATAGATGATTGTAATTATTCGTCTTGAACGAGGAATTCCTAGTAAGTGTGAGTCATCAGCTCGCGCTGATTACGTCCCTGCCCTTTGTACACACCGCCCGTCGCTCCTACCGATTGAATGGTCCGGTGAGAACGTCGGATCACGCGCGTGATACCTTCACCGGTAACTTGCGCGAGAGAAGTTGTTCAAACCTTACCATTTAGAGGAAGGAGAAGTCGTAACAAGGTTTCCGTAGGTGAACCTGCGGAAGGATCATT</t>
-  </si>
-  <si>
-    <t>GACGACTTTCAACGGTGGATCTCTTGGCTCGTGTATCGATGAAGAGCGCTGCGAACTGCGATACGTAATGCGAATTGCACAACTCAGTGAATCATCGAGATCTTGAACGCATATTGCGCTGCGACAGTCAATGTCGTAGCATGCCTGGTCGAGCATCTGTTCCAAACCTCAAAAAAAAATTCTAT--GTCTAAACCACATATTATTTTTACACTTTGAGGTCTCTCTTAGTGAGAAATTCTTTTTCTCGTTAAGGTAATTGATGAGAGTCAACACGCGATAAAAAGTGTGTCGTCTCTTTAAATTCATGGAATAGAAA--ACTCGTTTTAATTAATCCAAACAATTAAATTCGTTTTATCAAAAAAATATCACCAAAAAATGGCTTAATTTTTTGTGTGTTATTCATCCCATGTGGTAAACACCTCATGGTCTTTTGAATTAACATCACAATGTAAGTTATTTTGATATTTTATTCTTGAAAAAATTGAATTTTTTCCCGGATTAGATCTCGGCTCAGGCAAGGCTACCCGCTGAATTTAAGCATATAAT-TAAGCGGAGGAAAAGAAACTAACAAGGATTCCCTTAGTAACGGCGAGTGAAGCGGGAACAGCTCAAGCTTAAAACCTGTGCCCTTCGGGTACCGGATTGTAGCCTATAGAGGGAGCGTCCGGGCGAACGATGACCTAAATGCTTA--GGAATAAGCTGCCAAAGAGGGTGAGAGCCCCGTTCATGGTTGTCGACCTCGTCTATTGTGATGCCCTTTCATCGAGTCGGTCTGCTTGAGAGTGCAGACCTAAGTAGGTGGTATACTTCATCTAAAGCTAAATATTGACACGAGACCGATAGCGAACAAGTACCGTGAGGGAAAGATGAAAAGAACTTTGAAAAGAGAGTTAAACAGTACGTGAAACCGTTGAAAGGGAAGGTGATAAGCGCAGTGTCTCGTACGGCGAGCATTTTAGTCTAAACCTGCTGAAGGCTTGGTCAAGTCAGTGTCAAAGCGGCTTGGTTGAGTTTAGAGGTAGGGATGGGTGCACTATGCTTGTCGGGGCCTCTGGATGCGTTAGGCGAGCAGGAAATAACCATGATTGGGTAGGTTACCTTCGGGTACCGATGATTTCATGGCGAAACTGTTTGCGTGACGGAGGAAACAAAGGACTCGGCTCAGCCATGCAATTGTGTGCATTATGGGATTCATCAGGGCTTGCACTTCTTTGAAGTTCTTGTTTTGTTTGGGTTCTTGGTGTATGTCTTTGTATTGAGTTCTCTTGATCCAGAGTAAATGCTCTTATCACACCCGTCTTGAAACACGGACCAAGGAGTCTAACATGTATGCGAGTCGTAGGGTGGAAAACCTGAAGGCGCAATGAAAGTAAAGGCAGGCTCGGTCTGCTGAGGTGGGATCCCGACCCGAAAGGGGAAGGTGCACCATCAACCGATCATGATCCTCGGTGAATGATTTGAGTGATAGCATATCTGTTGGTACCCGAAAGATGGTGAACTATGCCTGTATAGGGTGAAGCCAGTGGAAACTCTGGTGGAGGCTCGTAGCGATACTGACGTGCAAATCGTTCGTCAAATATGGGTATAGGGGCGAAAGACTAATCGAACCATCTAGTAGCTGGTTCCCTCCGAAGTTTCCCTCAGGATAGCTGGAACTCGTTATACGCAGTCTTGTCAGGTAAAGCGAATGATTAGAGGATTTGGGGGTGAAACACTCTCGACCTATTCTCAAACTTTAAATGGGCAAGAAGTCCTTGTTGCTTAATTGAACTTGGACCTCGGATGCAGAGTTCTTAGTGGGCCATTTTTGGTAAGCAGAACTGGCGATGTGGGATGAACCGAACGCTGAGTTAAGGCGCCTAACTGCGCGCTCATCAGATACCATAAAAGGTGTTGGTTGATATAGACAGCAGGACGGTGGCCATGGAAGTCGGAACCCGCTAAGGAGTGTGTAACAACTCACCTGCCGAATCAACTAGCCCT-GAAAATGGATGGCGCTTAAGCGCGTGGCCTATACTCAGCCGTCATTGCAAATGCGATGCTTTGACGAGTAGGAGGGCGTGGTGGTTGCGACGCAACCTTGGGCGTAAGCCCGGGTGAAGCGGCCACTAGTGCAGATCTTGGTGGTAGTAGCAAATATTCAAATGAGAACTTTGAAGACTGAAGTGGAGAAAGGTTCCATGTGAACATTGATTGGACATGGGTTAGTCGATCCTAAGAGATAGGCGAACGCC-GTTCTGAATTGGTGTTATTCGTAGCACCTCCTATCGAAAGGGAATGGGGTTAATATTCCCCAACCTGCGGAAGATAATTTATTGCGGTAACGCGAACGAACACGGAGACGTCGGCCGAGACCCCTGGAAGAGTTCTCTTTTCTTGTTAACAAGTTAGCGGCCGTGGAATCAGATTAACTGGAGATACGGCTGTATGCTTGGGAAAGCAGATCGATTCTTGATCTGTCAGGTGCGTTTCGGACGGCCCTTGAAAATCCGTGGGAGAGTGTAACTTTTTCCGTTGGTCGTACTCATAACCGCATCAGGTCTCCAAGGTGATCAGCCTCTAGTCAATAGAATAATGTAGATAAGGGAAGTCGGCAAAATAGATCCGTAACTTCGGGAAAAGGATTGGCTCTGAAGGCTGGGTCGAGGGGTCCGCTTTCTAAAGCTGGATGGACCGATGGGGTACTGGAATGATGATCTTCGGGTTGTTGCTCTGGAACCTGTTGGTCTTCTGGTGGAGGGTTGTGGAACGAGGGGTGCAGCAATGTGCTCTTTTTCCTTCGGCAATTAACAGCCAGTTCAGAACTGTTTCGGACAAGGGGAATCCGACTGTTTAATTAAAACAAAGCATTGCGATGGTCGTTGGTCGGTGTTGACGCAATGTGATTTCTGCCCAGTGCTCTGAATGTCAAAGTGAAGAGATTCAACCAAGCGCGGGTAAACGGCGGGAGTAACTATGACTCTCTTAAGGTAGCCAAATGCCT--CGTCATCTAATTAGTGACGCGCATGAATGGATTAATGAGATTCCCACTGTCCCTATCTACTATCTAGCGAAACCACAGCCAAGGGAACGGGCTTGGAAACATCAGCGGGGAAAGAAGACCCTGTTGAGCTTGACTCTAGTCAGACTTTGTGAATTGACTTGGGAGGTGTAGAATAAGTGGGAGCTTCGGCGCCAATGAAATACCACTACTTCCAATGTTAATTTGCTTATTTAATCATGCAGGGCCGGTCTTCGGACCATTTTGTGGCTTTAAGCATTTTCCTTCACGGGAGGGTGCGACCTGTGTTAAAGACATAGTCTGGTGGGGAGTTTGGCTGGGGCGGCACATCTGTTAAAAGATAACGCAGGTGTCCTAAGATGGTCTCAATGAGAACAGAAATCTCATGTAGAGGAAAAGGCCAAAGTGACCATTTGATTTTGATTTTCAGTACGAATACAAACTGTGAAAGCATGGCCTATCGATCCTTTAGTTCTTGGAAGCATCAAGCTAGAGGTGTCAGAAAAGTTACCACAGGGATAACTGGCTTGTGGCAGCCAAGCGTTCATAGCGACGTTGCTTTTTGATCCTTCGATGTCGGCTCTTCCTATCATTGCGAAGCAGAATTCGCCAAGTGTTGGATTGTTCACCCACTAATAGGGAACGTGAGCTGGGTTTAGACCGTCGTGAGACAGGTTAGTTTTACCCTACTGATAAATTGTCGCAACAGTAATCCAGTCTAGTACGAGAGGAACCGCTGGTTCAGACATTTGGTATATACTCCTGGCTGAAAAGCCAATGGGGTGATGCTACCATCTGCAGGATTATGGCTGAACGCCTCTAAGTCAGAATCCATGCTGGAAAGTGACGAGACTTCATCCCTTCAGACTGAGATGTGTACTCATAGACCTTCGGGTCCAAGACCGTGTGACAGAATACTGGCTATGGCGGAAAAAGTTATGGTCAGCTCTGTTAATCGCAACTTGCAATGTTTGAAGGGGTAAATCCTTTGCATACGACTTAAATAAAGGAACAGGGTATTGTAAGTAGTTAGAGTGGCCTAGTTGCTGCGATCTACTGAGATTAAGCCCGCGTT</t>
   </si>
   <si>
     <t>annotation</t>
@@ -2680,6 +2659,12 @@
   </si>
   <si>
     <t>Contaminated_Arcella_vulgaris_trans</t>
+  </si>
+  <si>
+    <t>Gerasimova et al</t>
+  </si>
+  <si>
+    <t>unpublished_by_request</t>
   </si>
 </sst>
 </file>
@@ -3216,13 +3201,13 @@
         <v>45</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>177</v>
@@ -3461,7 +3446,7 @@
         <v>42</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>214</v>
@@ -3496,7 +3481,7 @@
         <v>29</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>216</v>
@@ -3566,7 +3551,7 @@
         <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>220</v>
@@ -3636,7 +3621,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>224</v>
@@ -3671,7 +3656,7 @@
         <v>32</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>226</v>
@@ -4056,7 +4041,7 @@
         <v>35</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>248</v>
@@ -4091,7 +4076,7 @@
         <v>37</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>250</v>
@@ -4126,7 +4111,7 @@
         <v>37</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>252</v>
@@ -4161,7 +4146,7 @@
         <v>40</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>254</v>
@@ -4196,7 +4181,7 @@
         <v>35</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>256</v>
@@ -4336,7 +4321,7 @@
         <v>40</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>260</v>
@@ -4371,7 +4356,7 @@
         <v>37</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>263</v>
@@ -4476,7 +4461,7 @@
         <v>32</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>267</v>
@@ -4896,7 +4881,7 @@
         <v>32</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>290</v>
@@ -4931,7 +4916,7 @@
         <v>33</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>292</v>
@@ -5001,7 +4986,7 @@
         <v>32</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>296</v>
@@ -5036,7 +5021,7 @@
         <v>42</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>298</v>
@@ -5071,7 +5056,7 @@
         <v>29</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>300</v>
@@ -5106,7 +5091,7 @@
         <v>41</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>302</v>
@@ -5141,7 +5126,7 @@
         <v>42</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>304</v>
@@ -5176,7 +5161,7 @@
         <v>28</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>306</v>
@@ -5211,7 +5196,7 @@
         <v>33</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I58" s="8" t="s">
         <v>308</v>
@@ -5246,7 +5231,7 @@
         <v>28</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>310</v>
@@ -5281,7 +5266,7 @@
         <v>28</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>312</v>
@@ -5316,7 +5301,7 @@
         <v>24</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>314</v>
@@ -5351,7 +5336,7 @@
         <v>42</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>316</v>
@@ -5771,7 +5756,7 @@
         <v>35</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>180</v>
@@ -6065,7 +6050,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="10" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>67</v>
@@ -6074,28 +6059,28 @@
         <v>66</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>35</v>
       </c>
       <c r="H83" s="27" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K83" s="9" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6103,7 +6088,7 @@
         <v>336</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>66</v>
@@ -6115,7 +6100,7 @@
         <v>35</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>35</v>
@@ -6124,10 +6109,10 @@
         <v>78</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="K84" s="9" t="s">
         <v>35</v>
@@ -6138,7 +6123,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>66</v>
@@ -6150,7 +6135,7 @@
         <v>35</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>35</v>
@@ -6159,10 +6144,10 @@
         <v>60</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>344</v>
+        <v>387</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>35</v>
@@ -6173,7 +6158,7 @@
         <v>337</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>66</v>
@@ -6185,7 +6170,7 @@
         <v>35</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>35</v>
@@ -6194,10 +6179,10 @@
         <v>58</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="K86" s="9" t="s">
         <v>35</v>
@@ -6226,7 +6211,7 @@
         <v>35</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>35</v>
@@ -6261,7 +6246,7 @@
         <v>74</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>35</v>
@@ -6296,10 +6281,10 @@
         <v>35</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>335</v>
@@ -6310,10 +6295,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="24" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>66</v>
@@ -6325,19 +6310,19 @@
         <v>35</v>
       </c>
       <c r="F90" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H90" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="I90" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="G90" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H90" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>370</v>
-      </c>
       <c r="J90" s="9" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="K90" s="9" t="s">
         <v>35</v>
@@ -6345,10 +6330,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="25" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>66</v>
@@ -6360,19 +6345,19 @@
         <v>35</v>
       </c>
       <c r="F91" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="I91" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="J91" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="H91" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>35</v>
@@ -6380,10 +6365,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="25" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>66</v>
@@ -6395,19 +6380,19 @@
         <v>35</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="K92" s="9" t="s">
         <v>35</v>
@@ -6436,13 +6421,13 @@
         <v>35</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>332</v>
@@ -6468,16 +6453,16 @@
         <v>35</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="K94" s="9" t="s">
         <v>332</v>
@@ -6506,13 +6491,13 @@
         <v>35</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>35</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>332</v>
